--- a/Assets/Samples/MainDemo/Excels/Localizations/Texts/LocalizationTexts.xlsx
+++ b/Assets/Samples/MainDemo/Excels/Localizations/Texts/LocalizationTexts.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13140"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Demo_Localization" sheetId="3" r:id="rId1"/>
@@ -44,10 +44,10 @@
     <t>#Desc</t>
   </si>
   <si>
-    <t>#ChineseSimplified</t>
-  </si>
-  <si>
-    <t>#English</t>
+    <t>ChineseSimplified</t>
+  </si>
+  <si>
+    <t>English</t>
   </si>
   <si>
     <t>##type</t>
